--- a/handover/NIKE_Financial_Dataset_FY2020-2026.xlsx
+++ b/handover/NIKE_Financial_Dataset_FY2020-2026.xlsx
@@ -62,19 +62,19 @@
     <t>Thứ tự ưu tiên nguồn</t>
   </si>
   <si>
-    <t>(1) Báo cáo tài chính đã kiểm toán và thuyết minh (Item 8), đọc từ dữ liệu XBRL gắn trong chính 10-K. (2) Phần MD&amp;A (Item 7) của cùng 10-K cho số liệu non-GAAP và số do ban điều hành nêu: EBIT, tăng trưởng loại trừ tỷ giá, doanh số Digital. (3) API XBRL của SEC chỉ dùng để đối chiếu.</t>
+    <t>(1) Báo cáo tài chính đã kiểm toán và thuyết minh (Item 8), lấy từ dữ liệu XBRL đi kèm chính báo cáo 10-K. (2) Phần MD&amp;A (Item 7) của cùng báo cáo, cho các số non-GAAP và số do ban điều hành nêu: EBIT, tăng trưởng loại trừ tỷ giá, doanh số Digital. (3) Dữ liệu XBRL do SEC công bố chỉ dùng để đối chiếu.</t>
   </si>
   <si>
     <t>Quy tắc chọn số</t>
   </si>
   <si>
-    <t>Số của năm FY t lấy từ 10-K FY t. “Giá trị năm trước” là cột so sánh trong cùng 10-K đó và được dùng để tính tăng trưởng (cùng cơ sở NIKE dùng). Nếu 10-K năm sau trình bày lại, chênh lệch được ghi ở cột “Trình bày lại ở 10-K sau”, không thay thế số gốc.</t>
+    <t>Số liệu của mỗi năm tài chính được lấy từ báo cáo 10-K của chính năm đó. “Giá trị năm trước” là số ở cột so sánh trong cùng báo cáo, dùng để tính tăng trưởng giống cách NIKE tự tính. Nếu báo cáo năm sau trình bày lại số liệu, phần chênh lệch được ghi ở cột “Trình bày lại ở 10-K sau”, số gốc giữ nguyên.</t>
   </si>
   <si>
     <t>Tình trạng dữ liệu</t>
   </si>
   <si>
-    <t>Trích xuất tự động ngày 23/10/2026. 203 quan sát: 202 khớp nguồn chính thức, 1 không được công bố.</t>
+    <t>Trích xuất tự động ngày 23/10/2026. 203 số liệu: 202 khớp nguồn chính thức, 1 không được công bố.</t>
   </si>
   <si>
     <t>Cách sử dụng</t>
@@ -101,13 +101,13 @@
     <t>4. Xem chỉ số</t>
   </si>
   <si>
-    <t>Sheet 04 tính các tỷ lệ bằng công thức Excel từ sheet 02–03. Cột “Công thức” diễn giải từng chỉ số; mục D–E là kiểm tra đối chiếu.</t>
+    <t>Sheet 04 tính các tỷ lệ bằng công thức Excel từ sheet 02–03. Cột “Công thức” giải thích cách tính từng chỉ số, mục D–E là phần kiểm tra.</t>
   </si>
   <si>
     <t>5. Tra cứu</t>
   </si>
   <si>
-    <t>Sheet 05: danh mục 10-K, thuật ngữ, khoảng trống dữ liệu và các lần NIKE trình bày lại số liệu.</t>
+    <t>Sheet 05: danh mục 10-K, thuật ngữ, các số liệu còn thiếu và các lần NIKE trình bày lại số liệu.</t>
   </si>
   <si>
     <t>Quy ước trình bày</t>
@@ -140,7 +140,7 @@
     <t>Ô trống</t>
   </si>
   <si>
-    <t>Kèm trạng thái “Thiếu / không công bố”: NIKE không công bố số liệu đó. Không thay bằng 0. Ở sheet 04, “–” là không tính được do thiếu đầu vào.</t>
+    <t>Đi kèm trạng thái “Thiếu / không công bố”, nghĩa là NIKE không công bố số liệu đó. Ô để trống chứ không điền số 0. Ở sheet 04, “–” nghĩa là không tính được vì thiếu số đầu vào.</t>
   </si>
   <si>
     <t>Tỷ lệ %</t>
@@ -161,19 +161,19 @@
     <t>Không suy ra nhân quả</t>
   </si>
   <si>
-    <t>Các chỉ số cho thấy số liệu thay đổi cùng giai đoạn; không chứng minh thay đổi chiến lược kênh là nguyên nhân.</t>
+    <t>Các chỉ số chỉ cho thấy số liệu thay đổi trong cùng giai đoạn, không chứng minh việc thay đổi chiến lược kênh là nguyên nhân.</t>
   </si>
   <si>
     <t>Không có lợi nhuận theo kênh</t>
   </si>
   <si>
-    <t>NIKE không công bố lợi nhuận hay chi phí riêng của NIKE Direct và bán buôn; SG&amp;A là chi phí hợp nhất.</t>
+    <t>NIKE không công bố lợi nhuận hay chi phí riêng của NIKE Direct và bán buôn. SG&amp;A là chi phí chung của cả công ty.</t>
   </si>
   <si>
     <t>Không trộn phạm vi</t>
   </si>
   <si>
-    <t>Tỷ trọng kênh dùng mẫu số NIKE Brand; biên lợi nhuận dùng doanh thu NIKE, Inc.</t>
+    <t>Tỷ trọng các kênh tính trên doanh thu NIKE Brand, còn biên lợi nhuận tính trên doanh thu NIKE, Inc.</t>
   </si>
   <si>
     <t>Trích dẫn</t>
@@ -191,7 +191,7 @@
     <t>Dữ liệu tài chính hợp nhất – NIKE, Inc.</t>
   </si>
   <si>
-    <t>Báo cáo kết quả kinh doanh, hàng tồn kho, EBIT và tăng trưởng doanh thu NIKE công bố. Mỗi dòng: một chỉ tiêu × một năm tài chính.</t>
+    <t>Báo cáo kết quả kinh doanh, hàng tồn kho, EBIT và tăng trưởng doanh thu NIKE công bố. Mỗi dòng là một chỉ tiêu của một năm tài chính.</t>
   </si>
   <si>
     <t>Năm tài chính</t>
@@ -302,7 +302,7 @@
     <t>37,403</t>
   </si>
   <si>
-    <t>Khớp API XBRL của SEC (cùng số accession).</t>
+    <t>Khớp với dữ liệu XBRL do SEC công bố (cùng số accession).</t>
   </si>
   <si>
     <t>Không thay đổi khi trình bày lại trong 10-K FY2021, FY2022.</t>
@@ -1301,7 +1301,7 @@
     <t>Item 7 – MD&amp;A, bảng doanh thu NIKE, Inc., cột “% CHANGE EXCLUDING CURRENCY CHANGES”</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 31) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2020-bang-doanh-thu-tr31.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 31): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2020-bang-doanh-thu-tr31.png.</t>
   </si>
   <si>
     <t>TOTAL NIKE, INC. REVENUES – % change excluding currency changes</t>
@@ -1313,37 +1313,37 @@
     <t>FY2020|revenues_pct_change_cn</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 32) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2021-bang-doanh-thu-tr32.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 32): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2021-bang-doanh-thu-tr32.png.</t>
   </si>
   <si>
     <t>FY2021|revenues_pct_change_cn</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 32) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2022-bang-doanh-thu-tr32.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 32): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2022-bang-doanh-thu-tr32.png.</t>
   </si>
   <si>
     <t>FY2022|revenues_pct_change_cn</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 32) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2023-bang-doanh-thu-tr32.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 32): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2023-bang-doanh-thu-tr32.png.</t>
   </si>
   <si>
     <t>FY2023|revenues_pct_change_cn</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 34) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2024-bang-doanh-thu-tr34.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 34): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2024-bang-doanh-thu-tr34.png.</t>
   </si>
   <si>
     <t>FY2024|revenues_pct_change_cn</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 33) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2025-bang-doanh-thu-tr33.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 33): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2025-bang-doanh-thu-tr33.png.</t>
   </si>
   <si>
     <t>FY2025|revenues_pct_change_cn</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 32) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2026-bang-doanh-thu-tr32.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 32): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2026-bang-doanh-thu-tr32.png.</t>
   </si>
   <si>
     <t>FY2026|revenues_pct_change_cn</t>
@@ -1754,7 +1754,7 @@
     <t>Digital commerce sales were $5.5 billion for fiscal 2020 compared to $3.8 billion for fiscal 2019.</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 32) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2020-digital-tr32.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 32): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2020-digital-tr32.png.</t>
   </si>
   <si>
     <t>NIKE Brand Digital sales (FY2020–21: “Digital commerce sales”)</t>
@@ -1769,7 +1769,7 @@
     <t>Digital commerce sales were $9.1 billion for fiscal 2021 compared to $5.5 billion for fiscal 2020.</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 33) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2021-digital-tr33.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 33): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2021-digital-tr33.png.</t>
   </si>
   <si>
     <t>FY2021|nike_brand_digital_sales</t>
@@ -1778,7 +1778,7 @@
     <t>NIKE Brand Digital sales were $10.7 billion for fiscal 2022 compared to $9.1 billion for fiscal 2021.</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 33) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2022-digital-tr33.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 33): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2022-digital-tr33.png.</t>
   </si>
   <si>
     <t>FY2022|nike_brand_digital_sales</t>
@@ -1787,7 +1787,7 @@
     <t>NIKE Brand Digital sales were $12.6 billion for fiscal 2023 compared to $10.7 billion for fiscal 2022.</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 33) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2023-digital-tr33.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 33): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2023-digital-tr33.png.</t>
   </si>
   <si>
     <t>ĐIỀU CHỈNH HỒI TỐ: 10-K FY2024 trình bày lại là 12,4 tỷ USD (chênh −0,2 tỷ USD).</t>
@@ -1799,7 +1799,7 @@
     <t>NIKE Brand Digital sales were $12.1 billion for fiscal 2024 compared to $12.4 billion for fiscal 2023.</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 35) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2024-digital-tr35.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 35): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2024-digital-tr35.png.</t>
   </si>
   <si>
     <t>FY2024|nike_brand_digital_sales</t>
@@ -1808,7 +1808,7 @@
     <t>On a currency-neutral basis, NIKE Direct revenues decreased 12% due to declines in NIKE Brand Digital sales of 20% from $12.1 billion in fiscal 2024 to $9.6 billion in fiscal 2025, while NIKE store sales were flat.</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 34) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2025-digital-tr34.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 34): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2025-digital-tr34.png.</t>
   </si>
   <si>
     <t>FY2025|nike_brand_digital_sales</t>
@@ -1817,7 +1817,7 @@
     <t>NIKE Brand Digital sales were $8.6 billion in fiscal 2026 compared to $9.6 billion in fiscal 2025, with declines primarily due to reduced traffic.</t>
   </si>
   <si>
-    <t>Đọc lại trực tiếp trên trang 10-K (tr. 33) bằng cách thứ hai: khớp. Ảnh đối chiếu: handover/bang-chung-doi-chieu/FY2026-digital-tr33.png.</t>
+    <t>Đã đọc lại ngay trên trang 10-K (tr. 33): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2026-digital-tr33.png.</t>
   </si>
   <si>
     <t>FY2026|nike_brand_digital_sales</t>
@@ -2201,7 +2201,7 @@
     <t>Chỉ số tính toán (KPI) và kiểm tra đối chiếu</t>
   </si>
   <si>
-    <t>Mọi ô số trong sheet này là công thức Excel. Chữ xanh lá: lấy từ sheet 02/03 theo năm và mã chỉ tiêu; chữ đen: tính trong sheet này. Sửa số liệu ở sheet 02/03 thì sheet này tự cập nhật. “–” nghĩa là thiếu số liệu đầu vào, không phải bằng 0.</t>
+    <t>Mọi ô số trong sheet này là công thức Excel. Số màu xanh lá lấy từ sheet 02/03 theo năm và mã chỉ tiêu, số màu đen được tính ngay trong sheet này. Sửa số liệu ở sheet 02/03 thì sheet này tự cập nhật. “–” nghĩa là thiếu số liệu đầu vào, không phải bằng 0.</t>
   </si>
   <si>
     <t>Mã</t>
@@ -2372,7 +2372,7 @@
     <t>[Doanh thu Global Brand Divisions] / [Tổng doanh thu NIKE Brand]</t>
   </si>
   <si>
-    <t>Phần còn lại, chủ yếu là doanh thu cấp phép; dưới 0,3%.</t>
+    <t>Phần còn lại, chủ yếu là doanh thu cấp phép, dưới 0,3%.</t>
   </si>
   <si>
     <t>direct_growth</t>
@@ -2453,7 +2453,7 @@
     <t>[Tổng chi phí bán hàng và quản lý (SG&amp;A)] / [Doanh thu]</t>
   </si>
   <si>
-    <t>Chi phí hợp nhất; không phân bổ được theo kênh.</t>
+    <t>Chi phí chung của cả công ty, không phân bổ được theo kênh.</t>
   </si>
   <si>
     <t>demand_creation_ratio</t>
@@ -2465,7 +2465,7 @@
     <t>[Chi phí tạo nhu cầu] / [Doanh thu]</t>
   </si>
   <si>
-    <t>Cấu phần marketing của SG&amp;A.</t>
+    <t>Phần chi cho marketing trong SG&amp;A.</t>
   </si>
   <si>
     <t>operating_overhead_ratio</t>
@@ -2477,7 +2477,7 @@
     <t>[Chi phí vận hành chung] / [Doanh thu]</t>
   </si>
   <si>
-    <t>Cấu phần vận hành của SG&amp;A.</t>
+    <t>Phần chi phí vận hành trong SG&amp;A.</t>
   </si>
   <si>
     <t>ebit</t>
@@ -2489,7 +2489,7 @@
     <t>[Lợi nhuận sau thuế] + [Chi phí thuế thu nhập] + [Chi phí (thu nhập) lãi thuần]</t>
   </si>
   <si>
-    <t>Non-GAAP. NIKE không trình bày dòng “Operating income”; EBIT là thước đo NIKE dùng. Đối chiếu với EBIT do NIKE công bố.</t>
+    <t>Chỉ tiêu non-GAAP. NIKE không trình bày dòng “Operating income” mà dùng EBIT. Số tự tính được đối chiếu với EBIT do NIKE công bố.</t>
   </si>
   <si>
     <t>ebit_margin</t>
@@ -2570,7 +2570,7 @@
     <t>365 / Vòng quay hàng tồn kho.</t>
   </si>
   <si>
-    <t>D. Kiểm tra đối chiếu số học (kỳ vọng bằng 0; cột cuối là kết quả)</t>
+    <t>D. Kiểm tra các phép cộng trừ (đúng thì chênh lệch bằng 0, cột cuối là kết luận)</t>
   </si>
   <si>
     <t>chk_gross_profit</t>
@@ -2636,7 +2636,7 @@
     <t>[EBIT (tự tính theo định nghĩa của NIKE)] - [EBIT do NIKE công bố]   (ngưỡng ±1 triệu USD)</t>
   </si>
   <si>
-    <t>E. Đối chiếu với tỷ lệ NIKE tự công bố (chênh lệch; cột cuối là kết quả)</t>
+    <t>E. So với tỷ lệ NIKE tự công bố (các ô là phần chênh lệch, cột cuối là kết luận)</t>
   </si>
   <si>
     <t>cmp_revenue_growth</t>
@@ -2843,7 +2843,7 @@
     <t>Doanh thu cấp phép thương hiệu NIKE và doanh thu khác không thuộc khu vực địa lý.</t>
   </si>
   <si>
-    <t>Rất nhỏ (dưới 0,3% doanh thu NIKE Brand); không thuộc Direct hay Wholesale.</t>
+    <t>Rất nhỏ (dưới 0,3% doanh thu NIKE Brand), không thuộc Direct hay Wholesale.</t>
   </si>
   <si>
     <t>Phân khúc kinh doanh riêng của NIKE, Inc., có kênh trực tiếp và bán buôn riêng.</t>
@@ -2873,7 +2873,7 @@
     <t>Tổng của chi phí tạo nhu cầu (Demand creation) và chi phí vận hành chung (Operating overhead).</t>
   </si>
   <si>
-    <t>Chi phí hợp nhất. Không thể phân bổ tin cậy cho NIKE Direct hay Wholesale từ số liệu công bố.</t>
+    <t>Chi phí chung của cả công ty. Từ số liệu công bố, không thể phân bổ chính xác cho NIKE Direct hay Wholesale.</t>
   </si>
   <si>
     <t>EBIT</t>
@@ -2885,7 +2885,7 @@
     <t>Lợi nhuận sau thuế + Chi phí (thu nhập) lãi thuần + Chi phí thuế thu nhập (định nghĩa của NIKE).</t>
   </si>
   <si>
-    <t>Non-GAAP ở cấp NIKE, Inc. Đây là thước đo hiệu quả hoạt động NIKE dùng.</t>
+    <t>Chỉ tiêu non-GAAP, tính cho toàn NIKE, Inc. NIKE dùng chỉ tiêu này để đo hiệu quả hoạt động.</t>
   </si>
   <si>
     <t>Lợi nhuận hoạt động</t>
@@ -2897,7 +2897,7 @@
     <t>NIKE không trình bày dòng “Operating income” trên báo cáo kết quả kinh doanh.</t>
   </si>
   <si>
-    <t>Bộ dữ liệu không tự tạo chỉ tiêu này; dùng EBIT và ghi rõ là non-GAAP. Các trang tổng hợp bên thứ ba thường tự tính, không phải số NIKE công bố.</t>
+    <t>Bộ dữ liệu không tự tạo chỉ tiêu này mà dùng EBIT, có ghi rõ là non-GAAP. Các trang tổng hợp của bên thứ ba thường tự tính chỉ tiêu này, nên đó không phải số NIKE công bố.</t>
   </si>
   <si>
     <t>Tăng trưởng theo báo cáo</t>
@@ -2918,10 +2918,10 @@
     <t>Currency-neutral growth (% change excluding currency changes)</t>
   </si>
   <si>
-    <t>Tăng trưởng tính lại theo tỷ giá của năm trước để loại ảnh hưởng chuyển đổi ngoại tệ.</t>
-  </si>
-  <si>
-    <t>Non-GAAP do NIKE tính; không tự tính lại được từ BCTC. Lấy nguyên văn từ MD&amp;A.</t>
+    <t>Tăng trưởng tính lại theo tỷ giá của năm trước để loại bỏ ảnh hưởng của việc quy đổi ngoại tệ.</t>
+  </si>
+  <si>
+    <t>Chỉ tiêu non-GAAP do NIKE tính, không tự tính lại được từ BCTC. Số được lấy nguyên văn từ MD&amp;A.</t>
   </si>
   <si>
     <t>GAAP / Non-GAAP</t>
@@ -2966,13 +2966,13 @@
     <t>eXtensible Business Reporting Language</t>
   </si>
   <si>
-    <t>Thẻ dữ liệu máy đọc được gắn trực tiếp vào số liệu trong 10-K nộp SEC.</t>
-  </si>
-  <si>
-    <t>Cột “Thẻ XBRL” cho biết số liệu được lấy từ thẻ nào; dùng để kiểm tra tự động.</t>
-  </si>
-  <si>
-    <t>C. Khoảng trống dữ liệu và giới hạn</t>
+    <t>Nhãn dữ liệu (máy đọc được) gắn vào từng con số trong 10-K nộp SEC.</t>
+  </si>
+  <si>
+    <t>Cột “Thẻ XBRL” cho biết số liệu lấy từ thẻ nào, dùng cho việc kiểm tra tự động.</t>
+  </si>
+  <si>
+    <t>C. Số liệu còn thiếu và giới hạn</t>
   </si>
   <si>
     <t>Vấn đề</t>
@@ -2993,10 +2993,10 @@
     <t>Không công bố</t>
   </si>
   <si>
-    <t>NIKE không công bố lợi nhuận, biên gộp hay chi phí riêng của NIKE Direct và Wholesale; SG&amp;A là chi phí hợp nhất.</t>
-  </si>
-  <si>
-    <t>Không tính và không ước lượng. Mọi phân tích lợi nhuận chỉ ở phạm vi NIKE, Inc.</t>
+    <t>NIKE không công bố lợi nhuận, biên gộp hay chi phí riêng của NIKE Direct và Wholesale. SG&amp;A là chi phí chung của cả công ty.</t>
+  </si>
+  <si>
+    <t>Bộ dữ liệu không tính và không ước lượng các số này. Mọi phân tích lợi nhuận chỉ làm ở phạm vi NIKE, Inc.</t>
   </si>
   <si>
     <t>Tỷ trọng NIKE Direct FY2026 do NIKE nêu</t>
@@ -3008,7 +3008,7 @@
     <t>10-K FY2026 không có câu “approximately …% of total NIKE Brand revenues”.</t>
   </si>
   <si>
-    <t>Để trống, trạng thái “Thiếu / không công bố”. Tỷ trọng tự tính ở sheet 04 vẫn có đủ 7 năm.</t>
+    <t>Ô để trống, trạng thái “Thiếu / không công bố”. Tỷ trọng do nhóm tự tính ở sheet 04 vẫn có đủ 7 năm.</t>
   </si>
   <si>
     <t>Doanh số Digital</t>
@@ -3017,22 +3017,22 @@
     <t>Độ chính xác thấp</t>
   </si>
   <si>
-    <t>Chỉ công bố trong MD&amp;A, làm tròn 0,1 tỷ USD; FY2023 được trình bày lại từ 12,6 xuống 12,4 tỷ USD do phân loại lại giữa cửa hàng và Digital.</t>
-  </si>
-  <si>
-    <t>Giữ số gốc, ghi chú trình bày lại; tỷ trọng Digital/Direct ghi rõ là xấp xỉ.</t>
+    <t>Chỉ công bố trong MD&amp;A, làm tròn đến 0,1 tỷ USD. Số FY2023 được trình bày lại từ 12,6 xuống 12,4 tỷ USD do phân loại lại giữa cửa hàng và Digital.</t>
+  </si>
+  <si>
+    <t>Giữ số gốc và ghi chú việc trình bày lại. Tỷ trọng Digital trong NIKE Direct được ghi rõ là xấp xỉ.</t>
   </si>
   <si>
     <t>Không tự tính lại được</t>
   </si>
   <si>
-    <t>Do NIKE tính bằng tỷ giá nội bộ; không có dữ liệu để tính lại.</t>
+    <t>Do NIKE tính bằng tỷ giá nội bộ, bên ngoài không có dữ liệu để tính lại.</t>
   </si>
   <si>
     <t>Lấy nguyên văn từ bảng doanh thu trong MD&amp;A, rồi đọc lại trên trang 10-K để đối chiếu (ảnh chụp trong handover/bang-chung-doi-chieu/).</t>
   </si>
   <si>
-    <t>D. Các lần trình bày lại / phân loại lại NIKE công bố</t>
+    <t>D. Các lần NIKE trình bày lại hoặc phân loại lại số liệu</t>
   </si>
   <si>
     <t>Nội dung</t>
@@ -3077,13 +3077,13 @@
     <t>Ý nghĩa</t>
   </si>
   <si>
-    <t>Số quan sát hiện tại</t>
+    <t>Số lượng hiện tại</t>
   </si>
   <si>
     <t>Matched to official source</t>
   </si>
   <si>
-    <t>Số liệu lấy tự động từ 10-K và được kiểm tra chéo bằng ít nhất một cách thứ hai: dữ liệu XBRL do SEC công bố (xác nhận đọc đúng thẻ và đúng kỳ), bảng trong MD&amp;A, phép tính lại từ BCTC, hoặc đọc lại trực tiếp trên trang 10-K (có ảnh chụp đối chiếu).</t>
+    <t>Số liệu lấy tự động từ 10-K và đã được đối chiếu lại bằng ít nhất một cách khác: so với dữ liệu XBRL do SEC công bố (để chắc chắn đọc đúng chỉ tiêu và đúng kỳ), so với bảng trong MD&amp;A, tính lại từ báo cáo tài chính, hoặc đọc lại ngay trên trang 10-K (có ảnh chụp đối chiếu).</t>
   </si>
   <si>
     <t>Chờ người kiểm tra</t>
@@ -3092,7 +3092,7 @@
     <t>Pending human review</t>
   </si>
   <si>
-    <t>Số liệu chính thức nhưng chưa được kiểm tra chéo bằng cách thứ hai. Cần người mở 10-K đối chiếu.</t>
+    <t>Số liệu chính thức nhưng chưa được đối chiếu lại bằng cách khác. Cần một người mở 10-K để kiểm tra.</t>
   </si>
   <si>
     <t>Đã xác minh (người)</t>
@@ -3101,13 +3101,13 @@
     <t>Human verified</t>
   </si>
   <si>
-    <t>Thành viên nhóm đã tự mở 10-K, tìm đúng trang và xác nhận số liệu; ghi tên và ngày.</t>
+    <t>Thành viên nhóm đã tự mở 10-K, tìm đúng trang và xác nhận số liệu, có ghi tên và ngày.</t>
   </si>
   <si>
     <t>Missing or undisclosed</t>
   </si>
   <si>
-    <t>NIKE không công bố số liệu này trong 10-K tương ứng. Ô giá trị để trống, không thay bằng 0.</t>
+    <t>NIKE không công bố số liệu này trong báo cáo 10-K tương ứng. Ô giá trị để trống, không điền số 0.</t>
   </si>
   <si>
     <t>Bằng chứng mâu thuẫn</t>
@@ -3116,7 +3116,7 @@
     <t>Conflicting evidence</t>
   </si>
   <si>
-    <t>Hai nguồn chính thức cho kết quả khác nhau, lần đọc lại trên trang 10-K ra số khác, hoặc số đã xác minh khác số trích xuất mới. Không dùng cho đến khi giải quyết.</t>
+    <t>Hai nguồn chính thức cho kết quả khác nhau, lần đọc lại trên trang 10-K ra số khác, hoặc số đã xác minh khác số trích xuất mới. Chưa dùng số này cho đến khi xử lý xong.</t>
   </si>
   <si>
     <t>F. Kiểm tra tự động (lần chạy gần nhất)</t>
@@ -3134,13 +3134,13 @@
     <t>Ngày kiểm tra</t>
   </si>
   <si>
-    <t>Đối chiếu với API XBRL của SEC</t>
+    <t>Đối chiếu với dữ liệu XBRL của SEC</t>
   </si>
   <si>
     <t>247/247 khớp</t>
   </si>
   <si>
-    <t>Mọi giá trị hợp nhất (không chia theo kênh) của 7 báo cáo, kể cả cột so sánh, so với dữ liệu SEC theo cùng số accession.</t>
+    <t>Toàn bộ số hợp nhất (không chia theo kênh) của 7 báo cáo, kể cả cột năm trước, được so với dữ liệu SEC của đúng báo cáo đó (cùng số accession).</t>
   </si>
   <si>
     <t>23/10/2026</t>
@@ -3155,7 +3155,7 @@
     <t>Doanh thu NIKE Direct, bán buôn, Global Brand Divisions, NIKE Brand, Converse, Corporate và NIKE, Inc. ở hai vị trí khác nhau trong cùng 10-K.</t>
   </si>
   <si>
-    <t>Đối chiếu số học và tỷ lệ NIKE công bố</t>
+    <t>Kiểm tra cộng trừ và so với tỷ lệ NIKE công bố</t>
   </si>
   <si>
     <t>Đạt</t>
@@ -3170,7 +3170,7 @@
     <t>35/35 khớp</t>
   </si>
   <si>
-    <t>Các số chỉ có trong MD&amp;A: mở từng 10-K, tìm trang theo chân trang; 28 tỷ lệ tăng trưởng loại trừ tỷ giá đọc lại theo vị trí cột “% CHANGE EXCLUDING CURRENCY CHANGES” đầu tiên, 7 số Digital đọc lại từ câu văn trên đúng trang. Ảnh chụp và bảng so sánh: handover/bang-chung-doi-chieu/doi-chieu-35-so.html (cũng có trên dashboard web).</t>
+    <t>Các số chỉ có trong MD&amp;A: mở từng 10-K và tìm trang theo chân trang. 28 tỷ lệ tăng trưởng loại trừ tỷ giá được đọc lại theo vị trí cột “% CHANGE EXCLUDING CURRENCY CHANGES” đầu tiên, 7 số Digital được đọc lại từ câu văn trên đúng trang. Ảnh chụp và bảng so sánh: handover/bang-chung-doi-chieu/doi-chieu-35-so.html (cũng có trên dashboard web).</t>
   </si>
   <si>
     <t>24/10/2026</t>

--- a/handover/NIKE_Financial_Dataset_FY2020-2026.xlsx
+++ b/handover/NIKE_Financial_Dataset_FY2020-2026.xlsx
@@ -68,7 +68,7 @@
     <t>Quy tắc chọn số</t>
   </si>
   <si>
-    <t>Số liệu của mỗi năm tài chính được lấy từ báo cáo 10-K của chính năm đó. “Giá trị năm trước” là số ở cột so sánh trong cùng báo cáo, dùng để tính tăng trưởng giống cách NIKE tự tính. Nếu báo cáo năm sau trình bày lại số liệu, phần chênh lệch được ghi ở cột “Trình bày lại ở 10-K sau”, số gốc giữ nguyên.</t>
+    <t>Số liệu của mỗi năm tài chính được lấy từ báo cáo 10-K của chính năm đó. “Giá trị năm trước” là số của năm trước được in kèm trong cùng báo cáo để so sánh, dùng để tính tăng trưởng giống cách NIKE tự tính. Nếu báo cáo năm sau trình bày lại số liệu, phần chênh lệch được ghi ở cột “Trình bày lại ở 10-K sau”, số gốc giữ nguyên.</t>
   </si>
   <si>
     <t>Tình trạng dữ liệu</t>
@@ -1790,7 +1790,7 @@
     <t>Đã đọc lại ngay trên trang 10-K (tr. 33): khớp. Ảnh chụp đối chiếu: handover/bang-chung-doi-chieu/FY2023-digital-tr33.png.</t>
   </si>
   <si>
-    <t>ĐIỀU CHỈNH HỒI TỐ: 10-K FY2024 trình bày lại là 12,4 tỷ USD (chênh −0,2 tỷ USD).</t>
+    <t>CÓ THAY ĐỔI: 10-K FY2024 trình bày lại là 12,4 tỷ USD (chênh −0,2 tỷ USD).</t>
   </si>
   <si>
     <t>FY2023|nike_brand_digital_sales</t>
@@ -2942,7 +2942,7 @@
     <t>Comparative prior-year amount</t>
   </si>
   <si>
-    <t>Số của năm trước được trình bày làm cột so sánh trong 10-K của năm hiện tại.</t>
+    <t>Số của năm trước được in kèm trong 10-K năm hiện tại để so sánh.</t>
   </si>
   <si>
     <t>Dùng làm mẫu số khi tính tăng trưởng.</t>
